--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AC04A5-795C-48D8-B16F-726CC937CD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9506FC9-F000-4946-8592-D44ADE92B784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -233,10 +233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>APOL0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AGEO0001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -288,25 +284,146 @@
     <t>Market</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>AGEO0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEO0003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>트럼프 미 대통령, 중국에서 열린 시진핑 주석과의 회담 "매우 긍정적"이라고 평가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.investing.com/news/economy-news/trump-xi-call-for-improving-uschina-ties-as-beijing-talks-begin-4687087</t>
+  </si>
+  <si>
+    <t>UTC+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGEO0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우크라이나-러시아 전쟁 발발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ukraine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ukraine, Russia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=q23W-gxEpsQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTC-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>macro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMAC0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 채권 10년물 금리 4.5% 돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>United States</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>United States, Global</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTC+9</t>
+  </si>
+  <si>
+    <t>aperiodic</t>
+  </si>
+  <si>
+    <t>geopolitic</t>
+  </si>
+  <si>
+    <t>AGEO0005</t>
+  </si>
+  <si>
+    <t>인도 화물선, 호르무즈 인근 해역서 공격받아 폭발 후 침몰</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>India, Iran</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/001/0016079247</t>
+  </si>
+  <si>
+    <t>AGEO0006</t>
+  </si>
+  <si>
+    <t>다카이치 일본 총리 19일 경북 안동행…한일 정상 첫 고향방문 성사</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>South Korea, Japan</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/654/0000180760</t>
+  </si>
+  <si>
+    <t>UTC+8</t>
+  </si>
+  <si>
+    <t>AGEO0007</t>
+  </si>
+  <si>
+    <t>푸틴 러시아 대통령, 트럼프 방중 닷새만에 중국 방문</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>China, Russia</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/079/0004147387?sid=104</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -359,16 +476,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -376,10 +490,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -660,67 +780,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" style="1" customWidth="1"/>
-    <col min="8" max="10" width="8.796875" style="1"/>
-    <col min="11" max="11" width="10.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.77734375" style="1"/>
+    <col min="10" max="10" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" s="8" customFormat="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="K1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+    <row r="2" spans="1:12">
+      <c r="A2" s="10">
         <v>46154</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="10">
         <v>46154</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>0.46527777777777779</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -735,7 +856,7 @@
       <c r="G2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -748,14 +869,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3" spans="1:12">
+      <c r="A3" s="10">
         <v>45629</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="10">
         <v>45629</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>0.93541666666666667</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -770,7 +891,7 @@
       <c r="G3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -783,14 +904,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+    <row r="4" spans="1:12">
+      <c r="A4" s="10">
         <v>45629</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="10">
         <v>45629</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>0.98402777777777772</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -805,7 +926,7 @@
       <c r="G4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -821,14 +942,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5" spans="1:12">
+      <c r="A5" s="10">
         <v>46156</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="10">
         <v>46156</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>0.4513888888888889</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -838,12 +959,12 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -856,14 +977,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+    <row r="6" spans="1:12">
+      <c r="A6" s="10">
         <v>46156</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="10">
         <v>46156</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>0.49027777777777776</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -876,9 +997,9 @@
         <v>33</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -889,6 +1010,213 @@
       </c>
       <c r="L6" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="10">
+        <v>46156</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46156</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.99791666666666667</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="10">
+        <v>44616</v>
+      </c>
+      <c r="B8" s="10">
+        <v>44616</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.24305555555555555</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="10">
+        <v>46156</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46156</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="10">
+        <v>46155</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="10">
+        <v>46157</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="10">
+        <v>46157</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -900,36 +1228,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBA7BD2-AD12-462E-8AFC-3F954D612213}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="11.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15.6">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -939,11 +1267,11 @@
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15.6">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -953,11 +1281,11 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15.6">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -967,11 +1295,11 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.6">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -981,11 +1309,11 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.6">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -993,13 +1321,13 @@
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:4" ht="15.6">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1007,13 +1335,13 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1021,10 +1349,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1032,7 +1360,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9506FC9-F000-4946-8592-D44ADE92B784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEDD3D1-85EA-4B42-BC80-67BE8CF0EDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="111">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -403,6 +403,90 @@
   </si>
   <si>
     <t>https://n.news.naver.com/mnews/article/079/0004147387?sid=104</t>
+  </si>
+  <si>
+    <t>AGEO0008</t>
+  </si>
+  <si>
+    <t>다카이치 일본총리, 5월 19일 경북 안동에서 한일 정상회담 조율중(일 교도통신)</t>
+  </si>
+  <si>
+    <t>https://www.khan.co.kr/article/202605091144001</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/050/0000106273</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>ACOM0001</t>
+  </si>
+  <si>
+    <t>법원, 삼성 노조 총파업에 급제동, 사측이 제기한 위법 쟁의행위 금지 가처분 신청 대부분 인용. 위반시 하루 1억원 배상 판결</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>AMKT0001</t>
+  </si>
+  <si>
+    <t>AMKT0002</t>
+  </si>
+  <si>
+    <t>코스피200 선물 급락으로 프로그램매도 호가 효력 5분 정지(매도 사이드카 발동)</t>
+  </si>
+  <si>
+    <t>2거래일 연속 코스피200 선물 급락으로 프로그램매도 호가 효력 5분 정지(매도 사이드카 발동)</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/654/0000181048</t>
+  </si>
+  <si>
+    <t>politic</t>
+  </si>
+  <si>
+    <t>APOL0004</t>
+  </si>
+  <si>
+    <t>이재명 대통령, 노동권만큼 기업경영권도 존중되어야 한다고 발언, 삼성전자 긴급조정 가능성 열어두며 타협 압박</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/087/0001193828</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>AIND0001</t>
+  </si>
+  <si>
+    <t>https://biz.chosun.com/industry/company/2026/05/16/7ISVELGRZZBYFFZBSEL7IYJ3NM/</t>
+  </si>
+  <si>
+    <t>실전 검증 마친 천궁-II, 전 세계서 수입 문의 급증. 미국 패트리엇 미사일 틈새시장 공략. 업계에서는 조만간 카타르와 쿠웨이트 등에서 신규 계약이 체결될 것으로 전망</t>
+  </si>
+  <si>
+    <t>https://www.ytn.co.kr/_cs/_ln_0103_202605180510488951_005.html</t>
+  </si>
+  <si>
+    <t>AIND0002</t>
+  </si>
+  <si>
+    <t>AI로 쓴 서면으로 개인이 변호사 상대로 승소. 법률가도 놓친 실수를 인공지능이 잡아냄. 소액사건이지만, 법률 전문가인 변호사를 상대로 비전문가가 인공지능을 활용해 승소한 최초의 사건</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/119/0003091590</t>
+  </si>
+  <si>
+    <t>ACOM0002</t>
+  </si>
+  <si>
+    <t>삼성전자 노조 변호인, 법원 결정 존중한다면서 5월 21일 쟁의활동 계속 이어나갈것으로 입장 표명</t>
   </si>
 </sst>
 </file>
@@ -780,12 +864,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -1180,6 +1264,9 @@
       <c r="J11" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="K11" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L11" s="1" t="s">
         <v>76</v>
       </c>
@@ -1217,6 +1304,292 @@
       </c>
       <c r="L12" s="1" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="10">
+        <v>46151</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46151</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="10">
+        <v>46157</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.38819444444444445</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.2673611111111111</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.21527777777777779</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBA7BD2-AD12-462E-8AFC-3F954D612213}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -1363,6 +1736,28 @@
         <v>47</v>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEDD3D1-85EA-4B42-BC80-67BE8CF0EDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E706B2-30EF-46AE-AED3-D2FD1A7DAFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -487,6 +487,60 @@
   </si>
   <si>
     <t>삼성전자 노조 변호인, 법원 결정 존중한다면서 5월 21일 쟁의활동 계속 이어나갈것으로 입장 표명</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/015/0005288426?sid=101</t>
+  </si>
+  <si>
+    <t>정용진, '5·18 탱크데이' 스타벅스 대표 전격 경질</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/009/0005681906?sid=101</t>
+  </si>
+  <si>
+    <t>정용진, ‘탱크테이’ 스타벅스 이벤트에 “책임 통감” 사과문</t>
+  </si>
+  <si>
+    <t>ACOM0003</t>
+  </si>
+  <si>
+    <t>ACOM0004</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/057/0001949731</t>
+  </si>
+  <si>
+    <t>다카이치 일본 총리, 오늘 방한, 이 대통령 고향 안동서 회담</t>
+  </si>
+  <si>
+    <t>AGEO0009</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/277/0005764819?cds=news_media_pc&amp;type=breakingnews</t>
+  </si>
+  <si>
+    <t>ACOM0005</t>
+  </si>
+  <si>
+    <t>박수근 중노위원장 "삼성전자 노사 의견 일부 좁혀져"</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/056/0012183871</t>
+  </si>
+  <si>
+    <t>AGEO0010</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/001/0016086807</t>
+  </si>
+  <si>
+    <t>이재명 대통령, 다카이치 일본 총리와 정상회담</t>
+  </si>
+  <si>
+    <t>한일 정상은 안동 정상회담에서 공급망·LNG/원유 에너지 협력 확대, 한일·한미일 안보공조 및 한중일 협력 필요성, AI·우주·바이오 첨단기술 협력, 초국가 스캠범죄·개인정보보호 공동대응, 조세이 탄광 유해 DNA 감정 등 인도주의 협력을 논의하고 셔틀외교 정착을 재확인함.</t>
+  </si>
+  <si>
+    <t>AGEO0011</t>
   </si>
 </sst>
 </file>
@@ -864,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -874,7 +928,8 @@
     <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.77734375" style="1"/>
+    <col min="8" max="8" width="18.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="1"/>
     <col min="10" max="10" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.77734375" style="1"/>
@@ -1590,6 +1645,231 @@
       </c>
       <c r="L20" s="1" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B21" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.81666666666666665</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B22" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.37986111111111109</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B23" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.41944444444444445</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B26" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.71458333333333335</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E706B2-30EF-46AE-AED3-D2FD1A7DAFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B8DC4-4324-492B-B600-8097A8CC2B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="162">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -541,6 +541,105 @@
   </si>
   <si>
     <t>AGEO0011</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/ranking/article/417/0001144058</t>
+  </si>
+  <si>
+    <t>삼성전자 노조 "사측 거부로 조정 종료…내일 총파업"</t>
+  </si>
+  <si>
+    <t>ACOM0006</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>KRX:005930</t>
+  </si>
+  <si>
+    <t>KRX:004247, NASDAQ:SBUX</t>
+  </si>
+  <si>
+    <t>KRX:KOSPI</t>
+  </si>
+  <si>
+    <t>ICE:USDKRW</t>
+  </si>
+  <si>
+    <t>KRX:KOSPI, ICE:USDKRW</t>
+  </si>
+  <si>
+    <t>TVC:SPX, SSE:000001, SZSE:399001</t>
+  </si>
+  <si>
+    <t>TVC:US10Y</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/057/0001949967</t>
+  </si>
+  <si>
+    <t>중국 "미국과 각각 300억달러 이상 규모 상품관세 인하 논의할 것"</t>
+  </si>
+  <si>
+    <t>AGEO0012</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/article/031/0001029876</t>
+  </si>
+  <si>
+    <t>靑 "삼성 협상 결렬 매우 유감…끝까지 합의 최선 다하길"</t>
+  </si>
+  <si>
+    <t>APOL0005</t>
+  </si>
+  <si>
+    <t>https://www.joongang.co.kr/article/25429917?utm_source=navernewsstand&amp;utm_medium=referral&amp;utm_campaign=leftbottom1_newsstand&amp;utm_content=260520</t>
+  </si>
+  <si>
+    <t>블룸버그 “한국 유조선, 호르무즈해협 통과 시도 중” [출처:중앙일보] https://www.joongang.co.kr/article/25429917</t>
+  </si>
+  <si>
+    <t>AGEO0013</t>
+  </si>
+  <si>
+    <t>https://www.donga.com/news/NewsStand/article/all/20260520/133960442/2</t>
+  </si>
+  <si>
+    <t>삼전 노사, 대화 재개…노동장관 직접 조정 ‘이례적’</t>
+  </si>
+  <si>
+    <t>ACOM0007</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/news/economy-news/article-1953247</t>
+  </si>
+  <si>
+    <t>베선트 "美中 관세 휴전 연장, 서두르지 않는다...중국, 기존 관세 복원 수용 가능”</t>
+  </si>
+  <si>
+    <t>AGEO0014</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>United States, China</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/news/economy-news/article-93CH-1952593</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>AMAC0002</t>
+  </si>
+  <si>
+    <t>일본은행 우에다 총재, 금리 인상 시사하며 정부와 긴밀한 공조 약속</t>
+  </si>
+  <si>
+    <t>TVC:JP10Y</t>
   </si>
 </sst>
 </file>
@@ -918,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -932,10 +1031,11 @@
     <col min="9" max="9" width="8.77734375" style="1"/>
     <col min="10" max="10" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="1"/>
+    <col min="12" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="8" customFormat="1">
+    <row r="1" spans="1:13" s="8" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -970,10 +1070,13 @@
         <v>43</v>
       </c>
       <c r="L1" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="10">
         <v>46154</v>
       </c>
@@ -1005,10 +1108,13 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="10">
         <v>45629</v>
       </c>
@@ -1040,10 +1146,13 @@
         <v>21</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="10">
         <v>45629</v>
       </c>
@@ -1078,10 +1187,13 @@
         <v>40</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="10">
         <v>46156</v>
       </c>
@@ -1112,11 +1224,11 @@
       <c r="J5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="10">
         <v>46156</v>
       </c>
@@ -1147,11 +1259,11 @@
       <c r="J6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="10">
         <v>46156</v>
       </c>
@@ -1183,10 +1295,13 @@
         <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="10">
         <v>44616</v>
       </c>
@@ -1217,11 +1332,11 @@
       <c r="J8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="10">
         <v>46156</v>
       </c>
@@ -1252,8 +1367,11 @@
       <c r="J9" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="10">
         <v>46155</v>
       </c>
@@ -1284,11 +1402,11 @@
       <c r="J10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="10">
         <v>46157</v>
       </c>
@@ -1322,11 +1440,11 @@
       <c r="K11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="10">
         <v>46157</v>
       </c>
@@ -1357,11 +1475,11 @@
       <c r="J12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="10">
         <v>46151</v>
       </c>
@@ -1392,11 +1510,11 @@
       <c r="J13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="10">
         <v>46160</v>
       </c>
@@ -1428,10 +1546,13 @@
         <v>74</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="10">
         <v>46157</v>
       </c>
@@ -1462,8 +1583,11 @@
       <c r="J15" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="L15" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="10">
         <v>46160</v>
       </c>
@@ -1498,10 +1622,13 @@
         <v>91</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="10">
         <v>46160</v>
       </c>
@@ -1536,10 +1663,13 @@
         <v>88</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="10">
         <v>46160</v>
       </c>
@@ -1570,11 +1700,11 @@
       <c r="J18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="10">
         <v>46160</v>
       </c>
@@ -1605,11 +1735,11 @@
       <c r="J19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="10">
         <v>46160</v>
       </c>
@@ -1644,10 +1774,13 @@
         <v>97</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="10">
         <v>46160</v>
       </c>
@@ -1679,10 +1812,13 @@
         <v>74</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="10">
         <v>46161</v>
       </c>
@@ -1717,10 +1853,13 @@
         <v>115</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:13">
       <c r="A23" s="10">
         <v>46161</v>
       </c>
@@ -1754,11 +1893,11 @@
       <c r="K23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:13">
       <c r="A24" s="10">
         <v>46161</v>
       </c>
@@ -1793,10 +1932,13 @@
         <v>109</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:13">
       <c r="A25" s="10">
         <v>46161</v>
       </c>
@@ -1830,11 +1972,11 @@
       <c r="K25" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:13">
       <c r="A26" s="10">
         <v>46161</v>
       </c>
@@ -1868,8 +2010,283 @@
       <c r="K26" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B27" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B28" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.65763888888888888</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
